--- a/dosyalar/excel-klinigi/ExcelKlinigi_RITIM_Aliskanlik_Takibi.xlsx
+++ b/dosyalar/excel-klinigi/ExcelKlinigi_RITIM_Aliskanlik_Takibi.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Takip</t>
   </si>
   <si>
-    <t xml:space="preserve">Yaptığın günün hücresine 1 yaz. Bugünün satırı yeşil çerçevelidir.</t>
+    <t xml:space="preserve">Yaptığın günün hücresine 1 yaz. Bugünün satırı yeşil renklidir.</t>
   </si>
   <si>
     <t xml:space="preserve">Tarih</t>
